--- a/results/Int All Data -0.3/Rando_3_permute.xlsx
+++ b/results/Int All Data -0.3/Rando_3_permute.xlsx
@@ -440,247 +440,247 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7004666404905011</v>
+        <v>0.6904485041471964</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.698918363443115</v>
+        <v>0.6943360962132293</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6982528128591132</v>
+        <v>0.6916818042569348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6915217988491117</v>
+        <v>0.697782145266213</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7141832389121646</v>
+        <v>0.6974660896404229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7094107630064621</v>
+        <v>0.7307148538233741</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7094107630064621</v>
+        <v>0.7291345756944234</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7088106528364464</v>
+        <v>0.7284078994490061</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7081469000660157</v>
+        <v>0.727554657128187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7084313141729555</v>
+        <v>0.7165865560939408</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.683498156881527</v>
+        <v>0.7167444041254788</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.684035343576556</v>
+        <v>0.7195885451948758</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.684035343576556</v>
+        <v>0.7169022521570168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6817913126771745</v>
+        <v>0.717155024745106</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6843524778904887</v>
+        <v>0.7185454537609541</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6863433766390666</v>
+        <v>0.7154474614153252</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6922847909286642</v>
+        <v>0.7144360115002538</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6879872973684324</v>
+        <v>0.7322616926199034</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7094154373217468</v>
+        <v>0.7305868494971155</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7065709366896356</v>
+        <v>0.7175983655717263</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7037584371390889</v>
+        <v>0.7155441837854475</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7049273755229839</v>
+        <v>0.7128266087914522</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7069499157904123</v>
+        <v>0.7128266087914522</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6913384218648648</v>
+        <v>0.7128266087914522</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6964265938336432</v>
+        <v>0.7128266087914522</v>
       </c>
     </row>
     <row r="27">
@@ -690,997 +690,997 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6951623713304826</v>
+        <v>0.7156707498608492</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.686313173371073</v>
+        <v>0.7158915213673738</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6979123069687568</v>
+        <v>0.6690167685667399</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7004407519750779</v>
+        <v>0.6727777945573711</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6992085305534821</v>
+        <v>0.6720191172303891</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7041381353652942</v>
+        <v>0.6732207758212772</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7059395445634836</v>
+        <v>0.6732207758212772</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7025898583179081</v>
+        <v>0.6733157003778285</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7032219695694883</v>
+        <v>0.6729683627959022</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7066029377712002</v>
+        <v>0.6791629092363032</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7157663935428289</v>
+        <v>0.679857584400156</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7131433835426707</v>
+        <v>0.6696819595880275</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7131433835426707</v>
+        <v>0.6546367769373598</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7131433835426707</v>
+        <v>0.6504334888082509</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7127956863980303</v>
+        <v>0.643195491371214</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7134277976496104</v>
+        <v>0.6755600908399242</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.712858969435731</v>
+        <v>0.6870010168433558</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7139649843446394</v>
+        <v>0.687317072469146</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7139017013069385</v>
+        <v>0.6808697534406556</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7139017013069385</v>
+        <v>0.6797953800505976</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.706695345388752</v>
+        <v>0.6646567110942356</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7110564815493989</v>
+        <v>0.664751635650787</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7079908498480487</v>
+        <v>0.6653521053835167</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7097929781716668</v>
+        <v>0.6638034687734164</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7085923982689213</v>
+        <v>0.6643722969872959</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7075176653161491</v>
+        <v>0.6103587860587467</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7039155660451984</v>
+        <v>0.6160474277602551</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6988586760325562</v>
+        <v>0.6573870721383482</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.703978129957471</v>
+        <v>0.6612110216039662</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7071066851338077</v>
+        <v>0.6712295175099851</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7071066851338077</v>
+        <v>0.6723988154565943</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7018290236146407</v>
+        <v>0.6717667042050139</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6972143957404763</v>
+        <v>0.6984735843656379</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7015456881958437</v>
+        <v>0.6998956549003363</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7028099106990042</v>
+        <v>0.7034355498217288</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7021774398847098</v>
+        <v>0.6908569673905384</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7011347080135023</v>
+        <v>0.6990104114979526</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6994282233718641</v>
+        <v>0.6939542406107388</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6994282233718641</v>
+        <v>0.6990740540983678</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6980061528371655</v>
+        <v>0.6896571066132213</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6983222084629557</v>
+        <v>0.6878869793711679</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7017355373089464</v>
+        <v>0.684378725968626</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6989223186329714</v>
+        <v>0.6862114171229518</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7016402531896808</v>
+        <v>0.6824813135257426</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7016402531896808</v>
+        <v>0.684725344425124</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6862750597233669</v>
+        <v>0.6844092887993338</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6901939337455361</v>
+        <v>0.6963874014977944</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.695914576528609</v>
+        <v>0.6992635436487562</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6917432894810647</v>
+        <v>0.7013810084727359</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6823259824332041</v>
+        <v>0.7017287056173764</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.684411446175619</v>
+        <v>0.7113049393849176</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.685643667597215</v>
+        <v>0.7085244409159357</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.685643667597215</v>
+        <v>0.7104520566268127</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6750563434773167</v>
+        <v>0.7148135523501739</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6814389412172492</v>
+        <v>0.7197755178062647</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6823238250569188</v>
+        <v>0.7305214090831295</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6823238250569188</v>
+        <v>0.7292259046238327</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6829879373900637</v>
+        <v>0.7241373730923399</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6729050797582012</v>
+        <v>0.7220202678310745</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6718623478869937</v>
+        <v>0.7285305103345516</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6646254291380994</v>
+        <v>0.7267923841740629</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6730330840844598</v>
+        <v>0.7206934814156416</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6713578813989578</v>
+        <v>0.726130069654489</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6497111273154041</v>
+        <v>0.7268254639437701</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6482261333057189</v>
+        <v>0.7163974261062667</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6465192891013665</v>
+        <v>0.7181671937856058</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6475307390164378</v>
+        <v>0.7229716707728728</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6478471542049421</v>
+        <v>0.7226872566659333</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6478471542049421</v>
+        <v>0.6965837227397529</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6393456533901729</v>
+        <v>0.6976580961298108</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6473754079238994</v>
+        <v>0.6881782251696776</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6364738259917819</v>
+        <v>0.692348073966365</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6356835071459495</v>
+        <v>0.6915581146832468</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6356835071459495</v>
+        <v>0.6925062815606172</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6356835071459495</v>
+        <v>0.6883975584253454</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6353674515201593</v>
+        <v>0.6972751618391777</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6427000139510333</v>
+        <v>0.6972751618391777</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6440268003664663</v>
+        <v>0.7209462540037308</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6440268003664663</v>
+        <v>0.7209462540037308</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.648957483866421</v>
+        <v>0.7122865455947095</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5649291158065207</v>
+        <v>0.6936381849849487</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5664148289416343</v>
+        <v>0.6554569394884717</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5657194346523532</v>
+        <v>0.6383920930720894</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5477326694367378</v>
+        <v>0.6364331954050761</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5455522811377715</v>
+        <v>0.5371503791948384</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5615747552456605</v>
+        <v>0.5221400741274491</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.549154020846008</v>
+        <v>0.5221400741274491</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5496915671037511</v>
+        <v>0.5283975440428368</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5433388130690979</v>
+        <v>0.5493208579454011</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5408103680627768</v>
+        <v>0.5514074003759588</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5428951126797633</v>
+        <v>0.5599081820652995</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5415359656200515</v>
+        <v>0.5473285209459664</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5476025077341939</v>
+        <v>0.5456220363043282</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5472864521084039</v>
+        <v>0.5550724231218961</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5483924670173123</v>
+        <v>0.5164794783176492</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5585713278938687</v>
+        <v>0.5262459207610073</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5415366847454799</v>
+        <v>0.5311115234096901</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.552785963822238</v>
+        <v>0.5551630329258769</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5522473388763521</v>
+        <v>0.5652066982218904</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.551931283250562</v>
+        <v>0.5656489603603682</v>
       </c>
     </row>
     <row r="127">
@@ -1690,283 +1690,283 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5559450818292825</v>
+        <v>0.5656489603603682</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5164996138296449</v>
+        <v>0.5674187280397073</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5174477807070154</v>
+        <v>0.5674187280397073</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5168473109742855</v>
+        <v>0.6075268701216329</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5154568819584374</v>
+        <v>0.5857477969592501</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5243690033928338</v>
+        <v>0.6031941394154086</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5047102715561443</v>
+        <v>0.6031941394154086</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5056584384335148</v>
+        <v>0.5928268676766064</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5053423828077246</v>
+        <v>0.5928268676766064</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5127691506697215</v>
+        <v>0.5927010207266331</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5095769528929697</v>
+        <v>0.5881820365344482</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5095769528929697</v>
+        <v>0.588845789304879</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4984200814337635</v>
+        <v>0.5438382456791349</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4984200814337635</v>
+        <v>0.5397611640627135</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4987044955407032</v>
+        <v>0.5397611640627135</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4978512532198841</v>
+        <v>0.5395716745123251</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5004109801823414</v>
+        <v>0.5395716745123251</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4955759403643665</v>
+        <v>0.5421011982067888</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4872660864762711</v>
+        <v>0.538529661766546</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4872660864762711</v>
+        <v>0.538529661766546</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4810413367678764</v>
+        <v>0.5366016864929548</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4933649892346924</v>
+        <v>0.528256955021581</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4938705344108709</v>
+        <v>0.5129913604271029</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4880244042405388</v>
+        <v>0.5132757745340427</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4874555760266595</v>
+        <v>0.5094838261499894</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4570876283099546</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4800928103277917</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4863484824296084</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B156" t="n">
